--- a/eval-suite/cases/005_dwb_user_center_f/mapping.xlsx
+++ b/eval-suite/cases/005_dwb_user_center_f/mapping.xlsx
@@ -2,40 +2,387 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24980" windowHeight="11800" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实体级mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性级mapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="22">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+        <bgColor rgb="FF2563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -43,15 +390,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -404,7 +1065,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,478 +1074,598 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col width="14" customWidth="1" min="3" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>源表schema</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>源表物理表名</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>源表schema*</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表中文名</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>源表别名</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>目标表schema</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>源表物理表名*</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>源表别名*</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>目标表逻辑schema*</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>目标表中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>目标表物理表名</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>目标表物理名称*</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>取数规则</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>关联&amp;限定条件</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>数据库类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>用户维度表</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>dim_user_f</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>用户维度表</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>duf</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>场景1-用户基础属性</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>用户等级维度表</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>dim_user_level_f</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>用户等级维度表</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>dul</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>left join on u.level_id=ul.level_id</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>场景1-等级信息</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>地区维度表</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>dim_region_f</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>地区维度表</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>drf</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>left join on u.province_code=r.region_code</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>场景1-地区信息</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>用户来源维度表</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>dim_user_source_f</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>用户来源维度表</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>dus</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>left join on u.source_id=us.source_id</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>场景1-来源渠道</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>sdord</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>订单明细事实表</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>dwd_order_f</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>订单明细事实表</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>dof</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>left join on u.user_id=o.user_id AND o.order_status NOT IN ('CANCELLED','DELETED')</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>场景2-订单统计</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>sdlog</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>用户行为事实表</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>dwd_user_behavior_f</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>用户行为事实表</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>dub</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>left join on u.user_id=ub.user_id</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>场景2-行为数据</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>sdmar</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>优惠券使用事实表</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>dwd_coupon_use_f</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>优惠券使用事实表</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>dcu</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>left join on u.user_id=cu.user_id</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>场景2-优惠使用</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>sdref</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>退款事实表</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>dwd_refund_f</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>退款事实表</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>drf9</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>drf7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>left join on u.user_id=rf.user_id</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>场景2-退款统计</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>sdlog</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>购物车事实表</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>dwd_cart_f</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>购物车事实表</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>dcf</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>用户中心宽表</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>dwb_user_center_f</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>left join on u.user_id=c.user_id AND c.del_flag='N'</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>场景2-购物车</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -898,82 +1678,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O47"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>源Schema</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表物理表名</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>源表物理表别名</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>源表字段中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>源表字段名</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>源表字段类型</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>映射规则*</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>映射表达式</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>目标字段名*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>目标字段中文名</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>目标字段类型</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>数据标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="31" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -1042,8 +1836,9 @@
           <t>主键</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -1108,8 +1903,9 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -1174,8 +1970,9 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -1240,8 +2037,9 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -1306,8 +2104,9 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -1348,8 +2147,9 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -1414,8 +2214,9 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -1456,8 +2257,9 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -1522,8 +2324,9 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -1588,8 +2391,9 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -1654,8 +2458,9 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -1720,6 +2525,7 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1786,6 +2592,7 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1852,6 +2659,7 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1918,6 +2726,7 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1984,6 +2793,7 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2050,6 +2860,7 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2116,6 +2927,7 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2182,6 +2994,7 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2248,6 +3061,7 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2290,6 +3104,7 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2332,6 +3147,7 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2374,6 +3190,7 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2440,6 +3257,7 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2506,6 +3324,7 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2548,6 +3367,7 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2590,6 +3410,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2632,6 +3453,7 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2674,6 +3496,7 @@
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2740,6 +3563,7 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2806,6 +3630,7 @@
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2872,6 +3697,7 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2914,6 +3740,7 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2956,6 +3783,7 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2998,6 +3826,7 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3040,6 +3869,7 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3082,6 +3912,7 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3124,6 +3955,7 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3166,6 +3998,7 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3208,6 +4041,7 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3250,6 +4084,7 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3292,6 +4127,7 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3338,6 +4174,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3384,6 +4221,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3430,6 +4268,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3476,6 +4315,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/005_dwb_user_center_f/mapping.xlsx
+++ b/eval-suite/cases/005_dwb_user_center_f/mapping.xlsx
@@ -1195,10 +1195,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>主表</t>
@@ -1209,7 +1208,6 @@
           <t>场景1-用户基础属性</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1252,10 +1250,9 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>left join on u.level_id=ul.level_id</t>
@@ -1266,7 +1263,6 @@
           <t>场景1-等级信息</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4" ht="31" customHeight="1">
       <c r="A4" t="n">
@@ -1309,10 +1305,9 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>left join on u.province_code=r.region_code</t>
@@ -1323,7 +1318,6 @@
           <t>场景1-地区信息</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1366,10 +1360,9 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>left join on u.source_id=us.source_id</t>
@@ -1380,7 +1373,6 @@
           <t>场景1-来源渠道</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1423,10 +1415,9 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>left join on u.user_id=o.user_id AND o.order_status NOT IN ('CANCELLED','DELETED')</t>
@@ -1437,7 +1428,6 @@
           <t>场景2-订单统计</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1480,10 +1470,9 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>left join on u.user_id=ub.user_id</t>
@@ -1494,7 +1483,6 @@
           <t>场景2-行为数据</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1537,10 +1525,9 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>left join on u.user_id=cu.user_id</t>
@@ -1551,7 +1538,6 @@
           <t>场景2-优惠使用</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,10 +1580,9 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>left join on u.user_id=rf.user_id</t>
@@ -1608,7 +1593,6 @@
           <t>场景2-退款统计</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,10 +1635,9 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>dwb_user_center_f</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>dwb_user_center_i</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>left join on u.user_id=c.user_id AND c.del_flag='N'</t>
@@ -1665,7 +1648,6 @@
           <t>场景2-购物车</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1836,7 +1818,6 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
@@ -1902,8 +1883,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
@@ -1969,8 +1948,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
@@ -2036,8 +2013,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
@@ -2103,8 +2078,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
@@ -2115,12 +2088,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -2146,8 +2113,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
@@ -2213,8 +2178,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
@@ -2225,12 +2188,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -2256,8 +2213,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
@@ -2323,8 +2278,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
@@ -2390,8 +2343,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
@@ -2457,8 +2408,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
@@ -2524,8 +2473,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2591,8 +2538,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2658,8 +2603,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2725,8 +2668,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2792,8 +2733,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2859,8 +2798,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2926,8 +2863,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2993,8 +2928,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3060,8 +2993,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3072,12 +3003,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3103,8 +3028,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3115,12 +3038,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3146,8 +3063,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3158,12 +3073,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3189,8 +3098,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3256,8 +3163,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3323,8 +3228,6 @@
           <t>datetime</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3335,12 +3238,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3366,8 +3263,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3378,12 +3273,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3409,8 +3298,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3421,12 +3308,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3452,8 +3333,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3464,12 +3343,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3495,8 +3368,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3562,8 +3433,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3629,8 +3498,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3696,8 +3563,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3708,12 +3573,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3739,8 +3598,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3751,12 +3608,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3782,8 +3633,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3794,12 +3643,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3825,8 +3668,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3837,12 +3678,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3868,8 +3703,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3880,12 +3713,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3911,8 +3738,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3923,12 +3748,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3954,8 +3773,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3966,12 +3783,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -3997,8 +3808,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4009,12 +3818,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4040,8 +3843,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4052,12 +3853,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4083,8 +3878,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4095,12 +3888,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>数据加工</t>
@@ -4126,8 +3913,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4138,12 +3923,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -4174,7 +3953,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4185,12 +3963,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -4221,7 +3993,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4232,12 +4003,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -4268,7 +4033,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4279,12 +4043,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -4315,7 +4073,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/005_dwb_user_center_f/mapping.xlsx
+++ b/eval-suite/cases/005_dwb_user_center_f/mapping.xlsx
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
